--- a/dados/Analise_Atendimentos_Julho_2026.xlsx
+++ b/dados/Analise_Atendimentos_Julho_2026.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eduardo_Gastro_13-07" sheetId="1" r:id="Raa1770f97efa494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naira_Pediatria_13-07" sheetId="2" r:id="Rd150a1b00da6441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bruno_Neuro_13-07" sheetId="3" r:id="Rf8f58418980e4116"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Consolidada" sheetId="4" r:id="R26c9817a9ad94d62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emanuel_Obstetra_10-07" sheetId="5" r:id="Rad920223d7ba4578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fernanda_Gineco_10-07" sheetId="6" r:id="R5072e1557178404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marcelo_Cardio_10-07" sheetId="7" r:id="Rc586cde591f9426d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lucas_Ortopedia_16-07" sheetId="8" r:id="R0ec04c78b8074cd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vinicius_Ortopedia_16-07" sheetId="9" r:id="R4591a34dd87b4ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fernanda_Gineco_16-07" sheetId="10" r:id="R311ce974ffd2491c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Andre_Gineco_16-07" sheetId="11" r:id="R82dc382bfe60438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eduardo_Gastro_13-07" sheetId="1" r:id="R7204fd998a2e439e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Naira_Pediatria_13-07" sheetId="2" r:id="R5c5f11ce4a074a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bruno_Neuro_13-07" sheetId="3" r:id="Rea0b3c724fc04159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base Consolidada" sheetId="4" r:id="Rd4947b59420d4358"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emanuel_Obstetra_10-07" sheetId="5" r:id="Rc8c493a015074c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fernanda_Gineco_10-07" sheetId="6" r:id="Red7b8c9e9fe744de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marcelo_Cardio_10-07" sheetId="7" r:id="Rb70d085d35f44312"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lucas_Ortopedia_16-07" sheetId="8" r:id="R361164f21e474785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vinicius_Ortopedia_16-07" sheetId="9" r:id="R7e106800b9e843d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fernanda_Gineco_16-07" sheetId="10" r:id="R0de17d8a629146bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Andre_Gineco_16-07" sheetId="11" r:id="R66693140a66b4bff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,10 +219,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <x:numFmt numFmtId="165" formatCode="[h]:mm"/>
     <x:numFmt numFmtId="166" formatCode="hh:mm"/>
+    <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="6">
     <x:font>
@@ -258,7 +259,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="21">
+  <x:fills count="22">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -360,8 +361,21 @@
         <x:fgColor rgb="FFFFFDF0"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="29">
+  <x:borders count="32">
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
     <x:border/>
     <x:border/>
     <x:border/>
@@ -385,29 +399,15 @@
     <x:border/>
     <x:border>
       <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
       <x:right/>
       <x:top/>
     </x:border>
     <x:border>
       <x:left/>
-    </x:border>
-    <x:border>
       <x:right/>
     </x:border>
     <x:border>
       <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
       <x:right/>
       <x:bottom/>
     </x:border>
@@ -415,7 +415,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="270">
+  <x:cellXfs count="280">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -946,11 +946,27 @@
     <x:xf numFmtId="165" fontId="0" fillId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="165" fontId="0" fillId="20" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="165" fontId="0" fillId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="14">
+  <x:dxfs count="15">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9C0006"/>
@@ -1046,7 +1062,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1056,7 +1072,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1066,7 +1082,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1076,13 +1092,24 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:font>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
@@ -1176,8 +1203,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="BaseAtendimentos" displayName="BaseAtendimentos" ref="A2:M294" headerRowCount="1">
-  <x:tableColumns count="13">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="BaseAtendimentos" displayName="BaseAtendimentos" ref="A2:N294" headerRowCount="1">
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="Data"/>
     <x:tableColumn id="2" name="Médico"/>
     <x:tableColumn id="3" name="Especialidade"/>
@@ -1191,6 +1218,7 @@
     <x:tableColumn id="11" name="Intervalo seguinte"/>
     <x:tableColumn id="12" name="Origem"/>
     <x:tableColumn id="13" name="Tempo considerado"/>
+    <x:tableColumn id="14" name="Espera (min)"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -2465,7 +2493,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ed291582b504881"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce58588880dd4f31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3527,7 +3555,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba1a6c64e374c36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8848b449a3544fc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4763,7 +4791,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410dde7233974c4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9163d05ed6ec411d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5431,7 +5459,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6b39203f9c4ed4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R824bb48a05324ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6565,7 +6593,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ac29da840146a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32ec4a969dd145a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6588,6 +6616,7 @@
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="19.5">
@@ -6606,6 +6635,7 @@
       <x:c r="K1" s="50"/>
       <x:c r="L1" s="50"/>
       <x:c r="M1" t="str"/>
+      <x:c r="N1" t="str"/>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="92" t="str">
@@ -6647,6 +6677,9 @@
       <x:c r="M2" s="202" t="str">
         <x:v>Tempo considerado</x:v>
       </x:c>
+      <x:c r="N2" s="276" t="str">
+        <x:v>Espera (min)</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="154" t="n">
@@ -6688,6 +6721,9 @@
       <x:c r="M3" s="203" t="n">
         <x:v>0.015277777777777777</x:v>
       </x:c>
+      <x:c r="N3" s="277" t="n">
+        <x:v>13</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="28.5">
       <x:c r="A4" s="157" t="n">
@@ -6725,6 +6761,9 @@
       <x:c r="M4" s="47" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N4" s="278" t="n">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="28.5">
       <x:c r="A5" s="157" t="n">
@@ -6766,6 +6805,9 @@
       <x:c r="M5" s="47" t="n">
         <x:v>0.022222222222222223</x:v>
       </x:c>
+      <x:c r="N5" s="278" t="n">
+        <x:v>54</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="157" t="n">
@@ -6807,6 +6849,9 @@
       <x:c r="M6" s="47" t="n">
         <x:v>0.022916666666666665</x:v>
       </x:c>
+      <x:c r="N6" s="278" t="n">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="157" t="n">
@@ -6848,6 +6893,9 @@
       <x:c r="M7" s="47" t="n">
         <x:v>0.034722222222222224</x:v>
       </x:c>
+      <x:c r="N7" s="278" t="n">
+        <x:v>38</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="157" t="n">
@@ -6885,6 +6933,9 @@
       <x:c r="M8" s="47" t="n">
         <x:v>0.016666666666666666</x:v>
       </x:c>
+      <x:c r="N8" s="278" t="n">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="157" t="n">
@@ -6922,6 +6973,9 @@
       <x:c r="M9" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N9" s="278" t="n">
+        <x:v>8</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="157" t="n">
@@ -6959,6 +7013,9 @@
       <x:c r="M10" s="47" t="n">
         <x:v>0.0375</x:v>
       </x:c>
+      <x:c r="N10" s="278" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="157" t="n">
@@ -6996,6 +7053,9 @@
       <x:c r="M11" s="47" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N11" s="278" t="n">
+        <x:v>291</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="157" t="n">
@@ -7033,6 +7093,9 @@
       <x:c r="M12" s="47" t="n">
         <x:v>0.01597222222222222</x:v>
       </x:c>
+      <x:c r="N12" s="278" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="157" t="n">
@@ -7070,6 +7133,9 @@
       <x:c r="M13" s="47" t="n">
         <x:v>0.01597222222222222</x:v>
       </x:c>
+      <x:c r="N13" s="278" t="n">
+        <x:v>47</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="157" t="n">
@@ -7106,6 +7172,9 @@
       </x:c>
       <x:c r="M14" s="47" t="n">
         <x:v>0.013194444444444444</x:v>
+      </x:c>
+      <x:c r="N14" s="278" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -7142,6 +7211,9 @@
       <x:c r="M15" s="47" t="n">
         <x:v>0.014583333333333334</x:v>
       </x:c>
+      <x:c r="N15" s="278" t="n">
+        <x:v>203</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="157" t="n">
@@ -7179,6 +7251,9 @@
       <x:c r="M16" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N16" s="278" t="n">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="157" t="n">
@@ -7216,6 +7291,9 @@
       <x:c r="M17" s="47" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N17" s="278" t="n">
+        <x:v>44</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="157" t="n">
@@ -7253,6 +7331,9 @@
       <x:c r="M18" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N18" s="278" t="n">
+        <x:v>88</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="157" t="n">
@@ -7290,6 +7371,9 @@
       <x:c r="M19" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N19" s="278" t="n">
+        <x:v>72</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="157" t="n">
@@ -7327,6 +7411,9 @@
       <x:c r="M20" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N20" s="278" t="n">
+        <x:v>50</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="157" t="n">
@@ -7364,6 +7451,9 @@
       <x:c r="M21" s="47" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N21" s="278" t="n">
+        <x:v>121</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="157" t="n">
@@ -7401,6 +7491,9 @@
       <x:c r="M22" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N22" s="278" t="n">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="157" t="n">
@@ -7438,6 +7531,9 @@
       <x:c r="M23" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N23" s="278" t="n">
+        <x:v>132</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="157" t="n">
@@ -7475,6 +7571,9 @@
       <x:c r="M24" s="47" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N24" s="278" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="157" t="n">
@@ -7512,6 +7611,9 @@
       <x:c r="M25" s="47" t="n">
         <x:v>0.001388888888888889</x:v>
       </x:c>
+      <x:c r="N25" s="278" t="n">
+        <x:v>159</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="157" t="n">
@@ -7549,6 +7651,9 @@
       <x:c r="M26" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N26" s="278" t="n">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="157" t="n">
@@ -7586,6 +7691,9 @@
       <x:c r="M27" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N27" s="278" t="n">
+        <x:v>82</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="157" t="n">
@@ -7623,6 +7731,9 @@
       <x:c r="M28" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N28" s="278" t="n">
+        <x:v>65</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="157" t="n">
@@ -7660,6 +7771,9 @@
       <x:c r="M29" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N29" s="278" t="n">
+        <x:v>207</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="157" t="n">
@@ -7697,6 +7811,9 @@
       <x:c r="M30" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N30" s="278" t="n">
+        <x:v>70</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="157" t="n">
@@ -7734,6 +7851,9 @@
       <x:c r="M31" s="47" t="n">
         <x:v>0.001388888888888889</x:v>
       </x:c>
+      <x:c r="N31" s="278" t="n">
+        <x:v>53</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="157" t="n">
@@ -7771,6 +7891,9 @@
       <x:c r="M32" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N32" s="278" t="n">
+        <x:v>242</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="157" t="n">
@@ -7808,6 +7931,9 @@
       <x:c r="M33" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N33" s="278" t="n">
+        <x:v>29</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="157" t="n">
@@ -7845,6 +7971,9 @@
       <x:c r="M34" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N34" s="278" t="n">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="157" t="n">
@@ -7882,6 +8011,9 @@
       <x:c r="M35" s="47" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N35" s="278" t="n">
+        <x:v>278</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="157" t="n">
@@ -7919,6 +8051,9 @@
       <x:c r="M36" s="47" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N36" s="278" t="n">
+        <x:v>39</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="157" t="n">
@@ -7956,6 +8091,9 @@
       <x:c r="M37" s="47" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N37" s="278" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="157" t="n">
@@ -7993,6 +8131,9 @@
       <x:c r="M38" s="47" t="n">
         <x:v>0.001388888888888889</x:v>
       </x:c>
+      <x:c r="N38" s="278" t="n">
+        <x:v>20</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="157" t="n">
@@ -8030,6 +8171,9 @@
       <x:c r="M39" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N39" s="278" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="157" t="n">
@@ -8067,6 +8211,9 @@
       <x:c r="M40" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N40" s="278" t="n">
+        <x:v>43</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="157" t="n">
@@ -8104,6 +8251,9 @@
       <x:c r="M41" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N41" s="278" t="n">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="157" t="n">
@@ -8141,6 +8291,9 @@
       <x:c r="M42" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N42" s="278" t="n">
+        <x:v>67</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="157" t="n">
@@ -8178,6 +8331,9 @@
       <x:c r="M43" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N43" s="278" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="157" t="n">
@@ -8215,6 +8371,9 @@
       <x:c r="M44" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N44" s="278" t="n">
+        <x:v>83</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="157" t="n">
@@ -8252,6 +8411,9 @@
       <x:c r="M45" s="47" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N45" s="278" t="n">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="157" t="n">
@@ -8289,6 +8451,9 @@
       <x:c r="M46" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N46" s="278" t="n">
+        <x:v>47</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="157" t="n">
@@ -8326,6 +8491,9 @@
       <x:c r="M47" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N47" s="278" t="n">
+        <x:v>31</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="157" t="n">
@@ -8363,6 +8531,9 @@
       <x:c r="M48" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N48" s="278" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="157" t="n">
@@ -8400,6 +8571,9 @@
       <x:c r="M49" s="47" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N49" s="278" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="157" t="n">
@@ -8437,6 +8611,9 @@
       <x:c r="M50" s="47" t="n">
         <x:v>0.013888888888888888</x:v>
       </x:c>
+      <x:c r="N50" s="278" t="n">
+        <x:v>158</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="157" t="n">
@@ -8474,6 +8651,9 @@
       <x:c r="M51" s="47" t="n">
         <x:v>0.013194444444444444</x:v>
       </x:c>
+      <x:c r="N51" s="278" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="157" t="n">
@@ -8511,6 +8691,9 @@
       <x:c r="M52" s="47" t="n">
         <x:v>0.011111111111111112</x:v>
       </x:c>
+      <x:c r="N52" s="278" t="n">
+        <x:v>34</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="157" t="n">
@@ -8548,6 +8731,9 @@
       <x:c r="M53" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N53" s="278" t="n">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="157" t="n">
@@ -8585,6 +8771,9 @@
       <x:c r="M54" s="47" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N54" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="157" t="n">
@@ -8622,6 +8811,9 @@
       <x:c r="M55" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N55" s="278" t="n">
+        <x:v>54</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="157" t="n">
@@ -8659,6 +8851,9 @@
       <x:c r="M56" s="47" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N56" s="278" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="157" t="n">
@@ -8696,6 +8891,9 @@
       <x:c r="M57" s="47" t="n">
         <x:v>0.011111111111111112</x:v>
       </x:c>
+      <x:c r="N57" s="278" t="n">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="157" t="n">
@@ -8732,6 +8930,9 @@
       </x:c>
       <x:c r="M58" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
+      </x:c>
+      <x:c r="N58" s="278" t="n">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -8768,6 +8969,9 @@
       <x:c r="M59" s="47" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N59" s="278" t="n">
+        <x:v>85</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="157" t="n">
@@ -8805,6 +9009,9 @@
       <x:c r="M60" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N60" s="278" t="n">
+        <x:v>32</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="157" t="n">
@@ -8842,6 +9049,9 @@
       <x:c r="M61" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N61" s="278" t="n">
+        <x:v>41</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="157" t="n">
@@ -8879,6 +9089,9 @@
       <x:c r="M62" s="47" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N62" s="278" t="n">
+        <x:v>44</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="157" t="n">
@@ -8916,6 +9129,9 @@
       <x:c r="M63" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N63" s="278" t="n">
+        <x:v>58</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="157" t="n">
@@ -8953,6 +9169,9 @@
       <x:c r="M64" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N64" s="278" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="157" t="n">
@@ -8990,6 +9209,9 @@
       <x:c r="M65" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N65" s="278" t="n">
+        <x:v>113</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="157" t="n">
@@ -9027,6 +9249,9 @@
       <x:c r="M66" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N66" s="278" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="157" t="n">
@@ -9064,6 +9289,9 @@
       <x:c r="M67" s="47" t="n">
         <x:v>0.013888888888888888</x:v>
       </x:c>
+      <x:c r="N67" s="278" t="n">
+        <x:v>137</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="157" t="n">
@@ -9101,6 +9329,9 @@
       <x:c r="M68" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N68" s="278" t="n">
+        <x:v>128</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="157" t="n">
@@ -9138,6 +9369,9 @@
       <x:c r="M69" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N69" s="278" t="n">
+        <x:v>106</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="157" t="n">
@@ -9175,6 +9409,9 @@
       <x:c r="M70" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N70" s="278" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="157" t="n">
@@ -9212,6 +9449,9 @@
       <x:c r="M71" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N71" s="278" t="n">
+        <x:v>200</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="157" t="n">
@@ -9249,6 +9489,9 @@
       <x:c r="M72" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N72" s="278" t="n">
+        <x:v>211</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="157" t="n">
@@ -9286,6 +9529,9 @@
       <x:c r="M73" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N73" s="278" t="n">
+        <x:v>110</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="157" t="n">
@@ -9323,6 +9569,9 @@
       <x:c r="M74" s="47" t="n">
         <x:v>0.001388888888888889</x:v>
       </x:c>
+      <x:c r="N74" s="278" t="n">
+        <x:v>240</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="157" t="n">
@@ -9360,6 +9609,9 @@
       <x:c r="M75" s="47" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N75" s="278" t="n">
+        <x:v>116</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="157" t="n">
@@ -9397,6 +9649,9 @@
       <x:c r="M76" s="47" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N76" s="278" t="n">
+        <x:v>145</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="157" t="n">
@@ -9434,6 +9689,9 @@
       <x:c r="M77" s="47" t="n">
         <x:v>0.01875</x:v>
       </x:c>
+      <x:c r="N77" s="278" t="n">
+        <x:v>111</x:v>
+      </x:c>
     </x:row>
     <x:row r="78" ht="28.5">
       <x:c r="A78" s="157" t="n">
@@ -9471,6 +9729,9 @@
       <x:c r="M78" s="47" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N78" s="278" t="n">
+        <x:v>134</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="157" t="n">
@@ -9508,6 +9769,9 @@
       <x:c r="M79" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N79" s="278" t="n">
+        <x:v>151</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="157" t="n">
@@ -9545,6 +9809,9 @@
       <x:c r="M80" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N80" s="278" t="n">
+        <x:v>332</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="157" t="n">
@@ -9582,6 +9849,9 @@
       <x:c r="M81" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N81" s="278" t="n">
+        <x:v>107</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="157" t="n">
@@ -9619,6 +9889,9 @@
       <x:c r="M82" s="47" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N82" s="278" t="n">
+        <x:v>98</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="157" t="n">
@@ -9656,6 +9929,9 @@
       <x:c r="M83" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N83" s="278" t="n">
+        <x:v>76</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="157" t="n">
@@ -9693,6 +9969,9 @@
       <x:c r="M84" s="47" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N84" s="278" t="n">
+        <x:v>47</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="157" t="n">
@@ -9730,6 +10009,9 @@
       <x:c r="M85" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N85" s="278" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="157" t="n">
@@ -9767,6 +10049,9 @@
       <x:c r="M86" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N86" s="278" t="n">
+        <x:v>100</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="157" t="n">
@@ -9804,6 +10089,9 @@
       <x:c r="M87" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N87" s="278" t="n">
+        <x:v>104</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="157" t="n">
@@ -9841,6 +10129,9 @@
       <x:c r="M88" s="47" t="n">
         <x:v>0.018055555555555554</x:v>
       </x:c>
+      <x:c r="N88" s="278" t="n">
+        <x:v>41</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="157" t="n">
@@ -9878,6 +10169,9 @@
       <x:c r="M89" s="47" t="n">
         <x:v>0.0125</x:v>
       </x:c>
+      <x:c r="N89" s="278" t="n">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="157" t="n">
@@ -9915,6 +10209,9 @@
       <x:c r="M90" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N90" s="278" t="n">
+        <x:v>87</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="157" t="n">
@@ -9952,6 +10249,9 @@
       <x:c r="M91" s="47" t="n">
         <x:v>0.020833333333333332</x:v>
       </x:c>
+      <x:c r="N91" s="278" t="n">
+        <x:v>93</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="157" t="n">
@@ -9989,6 +10289,9 @@
       <x:c r="M92" s="47" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N92" s="278" t="n">
+        <x:v>110</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="157" t="n">
@@ -10026,6 +10329,9 @@
       <x:c r="M93" s="47" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N93" s="278" t="n">
+        <x:v>122</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="157" t="n">
@@ -10063,6 +10369,9 @@
       <x:c r="M94" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N94" s="278" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="157" t="n">
@@ -10100,6 +10409,9 @@
       <x:c r="M95" s="47" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N95" s="278" t="n">
+        <x:v>87</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="157" t="n">
@@ -10137,6 +10449,9 @@
       <x:c r="M96" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N96" s="278" t="n">
+        <x:v>97</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="157" t="n">
@@ -10174,6 +10489,9 @@
       <x:c r="M97" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N97" s="278" t="n">
+        <x:v>123</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="157" t="n">
@@ -10211,6 +10529,9 @@
       <x:c r="M98" s="47" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N98" s="278" t="n">
+        <x:v>267</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="157" t="n">
@@ -10248,6 +10569,9 @@
       <x:c r="M99" s="47" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N99" s="278" t="n">
+        <x:v>103</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="157" t="n">
@@ -10285,6 +10609,9 @@
       <x:c r="M100" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N100" s="278" t="n">
+        <x:v>82</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="157" t="n">
@@ -10322,6 +10649,9 @@
       <x:c r="M101" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N101" s="278" t="n">
+        <x:v>87</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="157" t="n">
@@ -10359,6 +10689,9 @@
       <x:c r="M102" s="47" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N102" s="278" t="n">
+        <x:v>81</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="157" t="n">
@@ -10396,6 +10729,9 @@
       <x:c r="M103" s="47" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N103" s="278" t="n">
+        <x:v>92</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="157" t="n">
@@ -10433,6 +10769,9 @@
       <x:c r="M104" s="47" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N104" s="278" t="n">
+        <x:v>66</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="157" t="n">
@@ -10469,6 +10808,9 @@
       </x:c>
       <x:c r="M105" s="47" t="n">
         <x:v>0.006944444444444444</x:v>
+      </x:c>
+      <x:c r="N105" s="278" t="n">
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -10505,6 +10847,9 @@
       <x:c r="M106" s="47" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N106" s="278" t="n">
+        <x:v>52</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="157" t="n">
@@ -10542,6 +10887,7 @@
       <x:c r="M107" s="47" t="n">
         <x:v>0.011111111110949423</x:v>
       </x:c>
+      <x:c r="N107" s="278"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="157" t="n">
@@ -10579,6 +10925,7 @@
       <x:c r="M108" s="47" t="n">
         <x:v>0.012500000004365575</x:v>
       </x:c>
+      <x:c r="N108" s="278"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="157" t="n">
@@ -10616,6 +10963,7 @@
       <x:c r="M109" s="47" t="n">
         <x:v>0.012499999997089617</x:v>
       </x:c>
+      <x:c r="N109" s="278"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="157" t="n">
@@ -10653,6 +11001,7 @@
       <x:c r="M110" s="47" t="n">
         <x:v>0.005555555551836733</x:v>
       </x:c>
+      <x:c r="N110" s="278"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="157" t="n">
@@ -10690,6 +11039,7 @@
       <x:c r="M111" s="47" t="n">
         <x:v>0.006944444445252884</x:v>
       </x:c>
+      <x:c r="N111" s="278"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="157" t="n">
@@ -10727,6 +11077,7 @@
       <x:c r="M112" s="47" t="n">
         <x:v>0.012500000004365575</x:v>
       </x:c>
+      <x:c r="N112" s="278"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="157" t="n">
@@ -10764,6 +11115,7 @@
       <x:c r="M113" s="47" t="n">
         <x:v>0.008333333338669036</x:v>
       </x:c>
+      <x:c r="N113" s="278"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="157" t="n">
@@ -10801,6 +11153,7 @@
       <x:c r="M114" s="47" t="n">
         <x:v>0.007638888884685002</x:v>
       </x:c>
+      <x:c r="N114" s="278"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="157" t="n">
@@ -10838,6 +11191,7 @@
       <x:c r="M115" s="47" t="n">
         <x:v>0.011805555557657499</x:v>
       </x:c>
+      <x:c r="N115" s="278"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="157" t="n">
@@ -10875,6 +11229,7 @@
       <x:c r="M116" s="47" t="n">
         <x:v>0.018055555556202307</x:v>
       </x:c>
+      <x:c r="N116" s="278"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="157" t="n">
@@ -10912,6 +11267,7 @@
       <x:c r="M117" s="47" t="n">
         <x:v>0.006944444445252884</x:v>
       </x:c>
+      <x:c r="N117" s="278"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="157" t="n">
@@ -10949,6 +11305,7 @@
       <x:c r="M118" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N118" s="278"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="157" t="n">
@@ -10986,6 +11343,7 @@
       <x:c r="M119" s="47" t="n">
         <x:v>0.004166666665696539</x:v>
       </x:c>
+      <x:c r="N119" s="278"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="157" t="n">
@@ -11023,6 +11381,7 @@
       <x:c r="M120" s="47" t="n">
         <x:v>0.004166666665696539</x:v>
       </x:c>
+      <x:c r="N120" s="278"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="157" t="n">
@@ -11060,6 +11419,7 @@
       <x:c r="M121" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N121" s="278"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="157" t="n">
@@ -11097,6 +11457,7 @@
       <x:c r="M122" s="47" t="n">
         <x:v>0.00972222222480923</x:v>
       </x:c>
+      <x:c r="N122" s="278"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="157" t="n">
@@ -11134,6 +11495,7 @@
       <x:c r="M123" s="47" t="n">
         <x:v>0.00555555555911269</x:v>
       </x:c>
+      <x:c r="N123" s="278"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="157" t="n">
@@ -11171,6 +11533,7 @@
       <x:c r="M124" s="47" t="n">
         <x:v>0.012499999997089617</x:v>
       </x:c>
+      <x:c r="N124" s="278"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="157" t="n">
@@ -11208,6 +11571,7 @@
       <x:c r="M125" s="47" t="n">
         <x:v>0.008333333331393078</x:v>
       </x:c>
+      <x:c r="N125" s="278"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="157" t="n">
@@ -11245,6 +11609,7 @@
       <x:c r="M126" s="47" t="n">
         <x:v>0.002777777779556345</x:v>
       </x:c>
+      <x:c r="N126" s="278"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="157" t="n">
@@ -11282,6 +11647,7 @@
       <x:c r="M127" s="47" t="n">
         <x:v>0.012499999997089617</x:v>
       </x:c>
+      <x:c r="N127" s="278"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="157" t="n">
@@ -11319,6 +11685,7 @@
       <x:c r="M128" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N128" s="278"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="157" t="n">
@@ -11356,6 +11723,7 @@
       <x:c r="M129" s="47" t="n">
         <x:v>0.011805555550381541</x:v>
       </x:c>
+      <x:c r="N129" s="278"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="157" t="n">
@@ -11393,6 +11761,7 @@
       <x:c r="M130" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N130" s="278"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="157" t="n">
@@ -11430,6 +11799,7 @@
       <x:c r="M131" s="47" t="n">
         <x:v>0.007638888884685002</x:v>
       </x:c>
+      <x:c r="N131" s="278"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="157" t="n">
@@ -11467,6 +11837,7 @@
       <x:c r="M132" s="47" t="n">
         <x:v>0.018055555556202307</x:v>
       </x:c>
+      <x:c r="N132" s="278"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="157" t="n">
@@ -11508,6 +11879,7 @@
       <x:c r="M133" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N133" s="278"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="157" t="n">
@@ -11545,6 +11917,7 @@
       <x:c r="M134" s="47" t="n">
         <x:v>0.004861111112404615</x:v>
       </x:c>
+      <x:c r="N134" s="278"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="157" t="n">
@@ -11582,6 +11955,7 @@
       <x:c r="M135" s="47" t="n">
         <x:v>0.008333333338669036</x:v>
       </x:c>
+      <x:c r="N135" s="278"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="157" t="n">
@@ -11619,6 +11993,7 @@
       <x:c r="M136" s="47" t="n">
         <x:v>0.011805555550381541</x:v>
       </x:c>
+      <x:c r="N136" s="278"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="157" t="n">
@@ -11656,6 +12031,7 @@
       <x:c r="M137" s="47" t="n">
         <x:v>0.0034722222189884633</x:v>
       </x:c>
+      <x:c r="N137" s="278"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="157" t="n">
@@ -11693,6 +12069,7 @@
       <x:c r="M138" s="47" t="n">
         <x:v>0.008333333331393078</x:v>
       </x:c>
+      <x:c r="N138" s="278"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="157" t="n">
@@ -11730,6 +12107,7 @@
       <x:c r="M139" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N139" s="278"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="157" t="n">
@@ -11765,6 +12143,7 @@
       <x:c r="M140" s="47" t="n">
         <x:v>0.01319444445107365</x:v>
       </x:c>
+      <x:c r="N140" s="278"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="157" t="n">
@@ -11802,6 +12181,7 @@
       <x:c r="M141" s="47" t="n">
         <x:v>0.012500000004365575</x:v>
       </x:c>
+      <x:c r="N141" s="278"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="157" t="n">
@@ -11843,6 +12223,7 @@
       <x:c r="M142" s="47" t="n">
         <x:v>0.003472222226264421</x:v>
       </x:c>
+      <x:c r="N142" s="278"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="157" t="n">
@@ -11884,6 +12265,7 @@
       <x:c r="M143" s="47" t="n">
         <x:v>0.018749999995634425</x:v>
       </x:c>
+      <x:c r="N143" s="278"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="157" t="n">
@@ -11921,6 +12303,7 @@
       <x:c r="M144" s="47" t="n">
         <x:v>0.010416666671517305</x:v>
       </x:c>
+      <x:c r="N144" s="278"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="157" t="n">
@@ -11958,6 +12341,7 @@
       <x:c r="M145" s="47" t="n">
         <x:v>0.011111111110949423</x:v>
       </x:c>
+      <x:c r="N145" s="278"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="157" t="n">
@@ -11995,6 +12379,7 @@
       <x:c r="M146" s="47" t="n">
         <x:v>0.008333333331393078</x:v>
       </x:c>
+      <x:c r="N146" s="278"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="157" t="n">
@@ -12032,6 +12417,7 @@
       <x:c r="M147" s="47" t="n">
         <x:v>0.013194444443797693</x:v>
       </x:c>
+      <x:c r="N147" s="278"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="157" t="n">
@@ -12069,6 +12455,7 @@
       <x:c r="M148" s="47" t="n">
         <x:v>0.005555555551836733</x:v>
       </x:c>
+      <x:c r="N148" s="278"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="157" t="n">
@@ -12106,6 +12493,7 @@
       <x:c r="M149" s="47" t="n">
         <x:v>0.004861111112404615</x:v>
       </x:c>
+      <x:c r="N149" s="278"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="157" t="n">
@@ -12143,6 +12531,7 @@
       <x:c r="M150" s="47" t="n">
         <x:v>0.008333333338669036</x:v>
       </x:c>
+      <x:c r="N150" s="278"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="157" t="n">
@@ -12180,6 +12569,7 @@
       <x:c r="M151" s="47" t="n">
         <x:v>0.006944444445252884</x:v>
       </x:c>
+      <x:c r="N151" s="278"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="157" t="n">
@@ -12217,6 +12607,7 @@
       <x:c r="M152" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N152" s="278"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="157" t="n">
@@ -12254,6 +12645,7 @@
       <x:c r="M153" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N153" s="278"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="157" t="n">
@@ -12291,6 +12683,7 @@
       <x:c r="M154" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N154" s="278"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="157" t="n">
@@ -12328,6 +12721,7 @@
       <x:c r="M155" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N155" s="278"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="157" t="n">
@@ -12365,6 +12759,7 @@
       <x:c r="M156" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N156" s="278"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="157" t="n">
@@ -12402,6 +12797,7 @@
       <x:c r="M157" s="47" t="n">
         <x:v>0.012499999997089617</x:v>
       </x:c>
+      <x:c r="N157" s="278"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="157" t="n">
@@ -12439,6 +12835,7 @@
       <x:c r="M158" s="47" t="n">
         <x:v>0.00972222222480923</x:v>
       </x:c>
+      <x:c r="N158" s="278"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="157" t="n">
@@ -12476,6 +12873,7 @@
       <x:c r="M159" s="47" t="n">
         <x:v>0.012500000004365575</x:v>
       </x:c>
+      <x:c r="N159" s="278"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="157" t="n">
@@ -12513,6 +12911,7 @@
       <x:c r="M160" s="47" t="n">
         <x:v>0.015277777776645962</x:v>
       </x:c>
+      <x:c r="N160" s="278"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="157" t="n">
@@ -12550,6 +12949,7 @@
       <x:c r="M161" s="47" t="n">
         <x:v>0.014583333337213844</x:v>
       </x:c>
+      <x:c r="N161" s="278"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="157" t="n">
@@ -12587,6 +12987,7 @@
       <x:c r="M162" s="47" t="n">
         <x:v>0.008333333331393078</x:v>
       </x:c>
+      <x:c r="N162" s="278"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="157" t="n">
@@ -12624,6 +13025,7 @@
       <x:c r="M163" s="47" t="n">
         <x:v>0.013888888890505768</x:v>
       </x:c>
+      <x:c r="N163" s="278"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="157" t="n">
@@ -12661,6 +13063,7 @@
       <x:c r="M164" s="47" t="n">
         <x:v>0.0062499999985448085</x:v>
       </x:c>
+      <x:c r="N164" s="278"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="157" t="n">
@@ -12698,6 +13101,7 @@
       <x:c r="M165" s="47" t="n">
         <x:v>0.010416666664241347</x:v>
       </x:c>
+      <x:c r="N165" s="278"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="157" t="n">
@@ -12735,6 +13139,7 @@
       <x:c r="M166" s="47" t="n">
         <x:v>0.013888888890505768</x:v>
       </x:c>
+      <x:c r="N166" s="278"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="157" t="n">
@@ -12772,6 +13177,7 @@
       <x:c r="M167" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N167" s="278"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="157" t="n">
@@ -12809,6 +13215,7 @@
       <x:c r="M168" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N168" s="278"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="157" t="n">
@@ -12846,6 +13253,7 @@
       <x:c r="M169" s="47" t="n">
         <x:v>0.006944444445252884</x:v>
       </x:c>
+      <x:c r="N169" s="278"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="157" t="n">
@@ -12883,6 +13291,7 @@
       <x:c r="M170" s="47" t="n">
         <x:v>0.013888888890505768</x:v>
       </x:c>
+      <x:c r="N170" s="278"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="157" t="n">
@@ -12918,6 +13327,7 @@
       <x:c r="M171" s="47" t="n">
         <x:v>0.006944444445252884</x:v>
       </x:c>
+      <x:c r="N171" s="278"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="157" t="n">
@@ -12955,6 +13365,7 @@
       <x:c r="M172" s="47" t="n">
         <x:v>0.030555555553291924</x:v>
       </x:c>
+      <x:c r="N172" s="278"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="157" t="n">
@@ -12992,6 +13403,7 @@
       <x:c r="M173" s="47" t="n">
         <x:v>0.010416666664241347</x:v>
       </x:c>
+      <x:c r="N173" s="278"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="157" t="n">
@@ -13029,6 +13441,7 @@
       <x:c r="M174" s="47" t="n">
         <x:v>0.011111111110949423</x:v>
       </x:c>
+      <x:c r="N174" s="278"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="157" t="n">
@@ -13066,6 +13479,7 @@
       <x:c r="M175" s="47" t="n">
         <x:v>0.006250000005820766</x:v>
       </x:c>
+      <x:c r="N175" s="278"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="157" t="n">
@@ -13103,6 +13517,7 @@
       <x:c r="M176" s="47" t="n">
         <x:v>0.018750000002910383</x:v>
       </x:c>
+      <x:c r="N176" s="278"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="157" t="n">
@@ -13140,6 +13555,7 @@
       <x:c r="M177" s="47" t="n">
         <x:v>0.007638888884685002</x:v>
       </x:c>
+      <x:c r="N177" s="278"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="157" t="n">
@@ -13177,6 +13593,7 @@
       <x:c r="M178" s="47" t="n">
         <x:v>0.008333333331393078</x:v>
       </x:c>
+      <x:c r="N178" s="278"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="157" t="n">
@@ -13214,6 +13631,7 @@
       <x:c r="M179" s="47" t="n">
         <x:v>0.005555555551836733</x:v>
       </x:c>
+      <x:c r="N179" s="278"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="157" t="n">
@@ -13251,6 +13669,7 @@
       <x:c r="M180" s="47" t="n">
         <x:v>0.009027777778101154</x:v>
       </x:c>
+      <x:c r="N180" s="278"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="157" t="n">
@@ -13288,6 +13707,7 @@
       <x:c r="M181" s="47" t="n">
         <x:v>0.014583333337213844</x:v>
       </x:c>
+      <x:c r="N181" s="278"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="157" t="n">
@@ -13325,6 +13745,7 @@
       <x:c r="M182" s="47" t="n">
         <x:v>0.010416666664241347</x:v>
       </x:c>
+      <x:c r="N182" s="278"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="157" t="n">
@@ -13362,6 +13783,7 @@
       <x:c r="M183" s="47" t="n">
         <x:v>0.00972222222480923</x:v>
       </x:c>
+      <x:c r="N183" s="278"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="157" t="n">
@@ -13399,6 +13821,7 @@
       <x:c r="M184" s="47" t="n">
         <x:v>0.006250000005820766</x:v>
       </x:c>
+      <x:c r="N184" s="278"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="157" t="n">
@@ -13436,6 +13859,7 @@
       <x:c r="M185" s="47" t="n">
         <x:v>0.015972222223354038</x:v>
       </x:c>
+      <x:c r="N185" s="278"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="157" t="n">
@@ -13473,6 +13897,7 @@
       <x:c r="M186" s="47" t="n">
         <x:v>0.00763888889196096</x:v>
       </x:c>
+      <x:c r="N186" s="278"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="157" t="n">
@@ -13510,6 +13935,7 @@
       <x:c r="M187" s="47" t="n">
         <x:v>0.004861111112404615</x:v>
       </x:c>
+      <x:c r="N187" s="278"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="157" t="n">
@@ -13547,6 +13973,7 @@
       <x:c r="M188" s="47" t="n">
         <x:v>0.005555555551836733</x:v>
       </x:c>
+      <x:c r="N188" s="278"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="159" t="n">
@@ -13582,6 +14009,7 @@
       <x:c r="M189" s="47" t="n">
         <x:v>0.005555555551836733</x:v>
       </x:c>
+      <x:c r="N189" s="278"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="264" t="n">
@@ -13619,6 +14047,9 @@
       <x:c r="M190" s="237" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N190" s="278" t="n">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="266" t="n">
@@ -13656,6 +14087,9 @@
       <x:c r="M191" s="242" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N191" s="278" t="n">
+        <x:v>84</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="266" t="n">
@@ -13693,6 +14127,9 @@
       <x:c r="M192" s="242" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N192" s="278" t="n">
+        <x:v>50</x:v>
+      </x:c>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="266" t="n">
@@ -13730,6 +14167,9 @@
       <x:c r="M193" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N193" s="278" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="266" t="n">
@@ -13767,6 +14207,9 @@
       <x:c r="M194" s="242" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N194" s="278" t="n">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="266" t="n">
@@ -13804,6 +14247,9 @@
       <x:c r="M195" s="242" t="n">
         <x:v>0.011805555555555555</x:v>
       </x:c>
+      <x:c r="N195" s="278" t="n">
+        <x:v>104</x:v>
+      </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="266" t="n">
@@ -13841,6 +14287,9 @@
       <x:c r="M196" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N196" s="278" t="n">
+        <x:v>53</x:v>
+      </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="266" t="n">
@@ -13878,6 +14327,9 @@
       <x:c r="M197" s="242" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N197" s="278" t="n">
+        <x:v>95</x:v>
+      </x:c>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="266" t="n">
@@ -13915,6 +14367,9 @@
       <x:c r="M198" s="242" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N198" s="278" t="n">
+        <x:v>99</x:v>
+      </x:c>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="266" t="n">
@@ -13952,6 +14407,9 @@
       <x:c r="M199" s="242" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N199" s="278" t="n">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="266" t="n">
@@ -13989,6 +14447,9 @@
       <x:c r="M200" s="242" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N200" s="278" t="n">
+        <x:v>77</x:v>
+      </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="266" t="n">
@@ -14026,6 +14487,9 @@
       <x:c r="M201" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N201" s="278" t="n">
+        <x:v>191</x:v>
+      </x:c>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="266" t="n">
@@ -14063,6 +14527,9 @@
       <x:c r="M202" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N202" s="278" t="n">
+        <x:v>120</x:v>
+      </x:c>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="266" t="n">
@@ -14100,6 +14567,9 @@
       <x:c r="M203" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N203" s="278" t="n">
+        <x:v>80</x:v>
+      </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="266" t="n">
@@ -14137,6 +14607,9 @@
       <x:c r="M204" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N204" s="278" t="n">
+        <x:v>118</x:v>
+      </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="266" t="n">
@@ -14174,6 +14647,9 @@
       <x:c r="M205" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N205" s="278" t="n">
+        <x:v>97</x:v>
+      </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="266" t="n">
@@ -14211,6 +14687,9 @@
       <x:c r="M206" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N206" s="278" t="n">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="266" t="n">
@@ -14247,6 +14726,9 @@
       </x:c>
       <x:c r="M207" s="242" t="n">
         <x:v>0.002777777777777778</x:v>
+      </x:c>
+      <x:c r="N207" s="278" t="n">
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -14283,6 +14765,9 @@
       <x:c r="M208" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N208" s="278" t="n">
+        <x:v>67</x:v>
+      </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="266" t="n">
@@ -14324,6 +14809,9 @@
       <x:c r="M209" s="242" t="n">
         <x:v>0.0006944444444444445</x:v>
       </x:c>
+      <x:c r="N209" s="278" t="n">
+        <x:v>16</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="266" t="n">
@@ -14361,6 +14849,9 @@
       <x:c r="M210" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N210" s="278" t="n">
+        <x:v>31</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="266" t="n">
@@ -14398,6 +14889,9 @@
       <x:c r="M211" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N211" s="278" t="n">
+        <x:v>27</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="266" t="n">
@@ -14435,6 +14929,9 @@
       <x:c r="M212" s="242" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N212" s="278" t="n">
+        <x:v>55</x:v>
+      </x:c>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="266" t="n">
@@ -14472,6 +14969,9 @@
       <x:c r="M213" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N213" s="278" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="266" t="n">
@@ -14509,6 +15009,9 @@
       <x:c r="M214" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N214" s="278" t="n">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="266" t="n">
@@ -14546,6 +15049,9 @@
       <x:c r="M215" s="242" t="n">
         <x:v>0.013194444444444444</x:v>
       </x:c>
+      <x:c r="N215" s="278" t="n">
+        <x:v>74</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="266" t="n">
@@ -14583,6 +15089,9 @@
       <x:c r="M216" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N216" s="278" t="n">
+        <x:v>94</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="266" t="n">
@@ -14620,6 +15129,9 @@
       <x:c r="M217" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N217" s="278" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="266" t="n">
@@ -14657,6 +15169,9 @@
       <x:c r="M218" s="242" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N218" s="278" t="n">
+        <x:v>133</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="266" t="n">
@@ -14694,6 +15209,9 @@
       <x:c r="M219" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N219" s="278" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="266" t="n">
@@ -14731,6 +15249,9 @@
       <x:c r="M220" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N220" s="278" t="n">
+        <x:v>145</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="266" t="n">
@@ -14772,6 +15293,9 @@
       <x:c r="M221" s="242" t="n">
         <x:v>0.011805555555555555</x:v>
       </x:c>
+      <x:c r="N221" s="278" t="n">
+        <x:v>153</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="266" t="n">
@@ -14813,6 +15337,9 @@
       <x:c r="M222" s="242" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N222" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="266" t="n">
@@ -14853,6 +15380,9 @@
       </x:c>
       <x:c r="M223" s="242" t="n">
         <x:v>0.009027777777777777</x:v>
+      </x:c>
+      <x:c r="N223" s="278" t="n">
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -14885,6 +15415,9 @@
         <x:v>Vinicius_Ortopedia_16-07</x:v>
       </x:c>
       <x:c r="M224" s="242"/>
+      <x:c r="N224" s="278" t="n">
+        <x:v>195</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="266" t="n">
@@ -14922,6 +15455,9 @@
       <x:c r="M225" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N225" s="278" t="n">
+        <x:v>24</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="266" t="n">
@@ -14959,6 +15495,9 @@
       <x:c r="M226" s="242" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N226" s="278" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="266" t="n">
@@ -14996,6 +15535,9 @@
       <x:c r="M227" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N227" s="278" t="n">
+        <x:v>49</x:v>
+      </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="266" t="n">
@@ -15033,6 +15575,9 @@
       <x:c r="M228" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N228" s="278" t="n">
+        <x:v>27</x:v>
+      </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="266" t="n">
@@ -15070,6 +15615,9 @@
       <x:c r="M229" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N229" s="278" t="n">
+        <x:v>89</x:v>
+      </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="266" t="n">
@@ -15107,6 +15655,9 @@
       <x:c r="M230" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N230" s="278" t="n">
+        <x:v>29</x:v>
+      </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="266" t="n">
@@ -15144,6 +15695,9 @@
       <x:c r="M231" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N231" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="266" t="n">
@@ -15181,6 +15735,9 @@
       <x:c r="M232" s="242" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N232" s="278" t="n">
+        <x:v>61</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="266" t="n">
@@ -15218,6 +15775,9 @@
       <x:c r="M233" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N233" s="278" t="n">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="266" t="n">
@@ -15255,6 +15815,9 @@
       <x:c r="M234" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N234" s="278" t="n">
+        <x:v>70</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="266" t="n">
@@ -15292,6 +15855,9 @@
       <x:c r="M235" s="242" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N235" s="278" t="n">
+        <x:v>165</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="266" t="n">
@@ -15329,6 +15895,9 @@
       <x:c r="M236" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N236" s="278" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="266" t="n">
@@ -15366,6 +15935,9 @@
       <x:c r="M237" s="242" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N237" s="278" t="n">
+        <x:v>191</x:v>
+      </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="266" t="n">
@@ -15403,6 +15975,9 @@
       <x:c r="M238" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N238" s="278" t="n">
+        <x:v>17</x:v>
+      </x:c>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="266" t="n">
@@ -15440,6 +16015,9 @@
       <x:c r="M239" s="242" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N239" s="278" t="n">
+        <x:v>210</x:v>
+      </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="266" t="n">
@@ -15477,6 +16055,9 @@
       <x:c r="M240" s="242" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N240" s="278" t="n">
+        <x:v>221</x:v>
+      </x:c>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="266" t="n">
@@ -15514,6 +16095,9 @@
       <x:c r="M241" s="242" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N241" s="278" t="n">
+        <x:v>235</x:v>
+      </x:c>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="266" t="n">
@@ -15551,6 +16135,9 @@
       <x:c r="M242" s="242" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N242" s="278" t="n">
+        <x:v>12</x:v>
+      </x:c>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="266" t="n">
@@ -15588,6 +16175,9 @@
       <x:c r="M243" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N243" s="278" t="n">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="266" t="n">
@@ -15625,6 +16215,9 @@
       <x:c r="M244" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N244" s="278" t="n">
+        <x:v>29</x:v>
+      </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="266" t="n">
@@ -15662,6 +16255,9 @@
       <x:c r="M245" s="242" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N245" s="278" t="n">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="266" t="n">
@@ -15699,6 +16295,9 @@
       <x:c r="M246" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N246" s="278" t="n">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="266" t="n">
@@ -15736,6 +16335,9 @@
       <x:c r="M247" s="242" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N247" s="278" t="n">
+        <x:v>25</x:v>
+      </x:c>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="266" t="n">
@@ -15773,6 +16375,9 @@
       <x:c r="M248" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N248" s="278" t="n">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="266" t="n">
@@ -15810,6 +16415,9 @@
       <x:c r="M249" s="242" t="n">
         <x:v>0.003472222222222222</x:v>
       </x:c>
+      <x:c r="N249" s="278" t="n">
+        <x:v>11</x:v>
+      </x:c>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="266" t="n">
@@ -15847,6 +16455,9 @@
       <x:c r="M250" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N250" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="266" t="n">
@@ -15884,6 +16495,9 @@
       <x:c r="M251" s="242" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N251" s="278" t="n">
+        <x:v>35</x:v>
+      </x:c>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="266" t="n">
@@ -15921,6 +16535,9 @@
       <x:c r="M252" s="242" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N252" s="278" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="266" t="n">
@@ -15958,6 +16575,9 @@
       <x:c r="M253" s="242" t="n">
         <x:v>0.005555555555555556</x:v>
       </x:c>
+      <x:c r="N253" s="278" t="n">
+        <x:v>14</x:v>
+      </x:c>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="266" t="n">
@@ -15995,6 +16615,9 @@
       <x:c r="M254" s="242" t="n">
         <x:v>0.008333333333333333</x:v>
       </x:c>
+      <x:c r="N254" s="278" t="n">
+        <x:v>75</x:v>
+      </x:c>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="266" t="n">
@@ -16031,6 +16654,9 @@
       </x:c>
       <x:c r="M255" s="242" t="n">
         <x:v>0.00625</x:v>
+      </x:c>
+      <x:c r="N255" s="278" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -16067,6 +16693,9 @@
       <x:c r="M256" s="242" t="n">
         <x:v>0.0020833333333333333</x:v>
       </x:c>
+      <x:c r="N256" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="266" t="n">
@@ -16104,6 +16733,9 @@
       <x:c r="M257" s="242" t="n">
         <x:v>0.0125</x:v>
       </x:c>
+      <x:c r="N257" s="278" t="n">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="266" t="n">
@@ -16141,6 +16773,9 @@
       <x:c r="M258" s="242" t="n">
         <x:v>0.015277777777777777</x:v>
       </x:c>
+      <x:c r="N258" s="278" t="n">
+        <x:v>42</x:v>
+      </x:c>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="266" t="n">
@@ -16178,6 +16813,9 @@
       <x:c r="M259" s="242" t="n">
         <x:v>0.01597222222222222</x:v>
       </x:c>
+      <x:c r="N259" s="278" t="n">
+        <x:v>56</x:v>
+      </x:c>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="266" t="n">
@@ -16215,6 +16853,9 @@
       <x:c r="M260" s="242" t="n">
         <x:v>0.021527777777777778</x:v>
       </x:c>
+      <x:c r="N260" s="278" t="n">
+        <x:v>59</x:v>
+      </x:c>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="266" t="n">
@@ -16252,6 +16893,9 @@
       <x:c r="M261" s="242" t="n">
         <x:v>0.022916666666666665</x:v>
       </x:c>
+      <x:c r="N261" s="278" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="266" t="n">
@@ -16289,6 +16933,9 @@
       <x:c r="M262" s="242" t="n">
         <x:v>0.014583333333333334</x:v>
       </x:c>
+      <x:c r="N262" s="278" t="n">
+        <x:v>138</x:v>
+      </x:c>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="266" t="n">
@@ -16326,6 +16973,9 @@
       <x:c r="M263" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N263" s="278" t="n">
+        <x:v>111</x:v>
+      </x:c>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="266" t="n">
@@ -16363,6 +17013,9 @@
       <x:c r="M264" s="242" t="n">
         <x:v>0.011805555555555555</x:v>
       </x:c>
+      <x:c r="N264" s="278" t="n">
+        <x:v>167</x:v>
+      </x:c>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="266" t="n">
@@ -16400,6 +17053,9 @@
       <x:c r="M265" s="242" t="n">
         <x:v>0.004166666666666667</x:v>
       </x:c>
+      <x:c r="N265" s="278" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="266" t="n">
@@ -16437,6 +17093,9 @@
       <x:c r="M266" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N266" s="278" t="n">
+        <x:v>191</x:v>
+      </x:c>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="266" t="n">
@@ -16474,6 +17133,9 @@
       <x:c r="M267" s="242" t="n">
         <x:v>0.011111111111111112</x:v>
       </x:c>
+      <x:c r="N267" s="278" t="n">
+        <x:v>202</x:v>
+      </x:c>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="266" t="n">
@@ -16511,6 +17173,9 @@
       <x:c r="M268" s="242" t="n">
         <x:v>0.018055555555555554</x:v>
       </x:c>
+      <x:c r="N268" s="278" t="n">
+        <x:v>128</x:v>
+      </x:c>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="266" t="n">
@@ -16548,6 +17213,9 @@
       <x:c r="M269" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N269" s="278" t="n">
+        <x:v>68</x:v>
+      </x:c>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="266" t="n">
@@ -16585,6 +17253,9 @@
       <x:c r="M270" s="242" t="n">
         <x:v>0.016666666666666666</x:v>
       </x:c>
+      <x:c r="N270" s="278" t="n">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="266" t="n">
@@ -16622,6 +17293,9 @@
       <x:c r="M271" s="242" t="n">
         <x:v>0.022222222222222223</x:v>
       </x:c>
+      <x:c r="N271" s="278" t="n">
+        <x:v>49</x:v>
+      </x:c>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="266" t="n">
@@ -16659,6 +17333,9 @@
       <x:c r="M272" s="242" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N272" s="278" t="n">
+        <x:v>324</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="266" t="n">
@@ -16696,6 +17373,9 @@
       <x:c r="M273" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N273" s="278" t="n">
+        <x:v>41</x:v>
+      </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="266" t="n">
@@ -16733,6 +17413,9 @@
       <x:c r="M274" s="242" t="n">
         <x:v>0.0125</x:v>
       </x:c>
+      <x:c r="N274" s="278" t="n">
+        <x:v>29</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="266" t="n">
@@ -16770,6 +17453,9 @@
       <x:c r="M275" s="242" t="n">
         <x:v>0.014583333333333334</x:v>
       </x:c>
+      <x:c r="N275" s="278" t="n">
+        <x:v>48</x:v>
+      </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="266" t="n">
@@ -16807,6 +17493,9 @@
       <x:c r="M276" s="242" t="n">
         <x:v>0.010416666666666666</x:v>
       </x:c>
+      <x:c r="N276" s="278" t="n">
+        <x:v>84</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="266" t="n">
@@ -16844,6 +17533,9 @@
       <x:c r="M277" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N277" s="278" t="n">
+        <x:v>69</x:v>
+      </x:c>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="266" t="n">
@@ -16881,6 +17573,9 @@
       <x:c r="M278" s="242" t="n">
         <x:v>0.004861111111111111</x:v>
       </x:c>
+      <x:c r="N278" s="278" t="n">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="266" t="n">
@@ -16918,6 +17613,9 @@
       <x:c r="M279" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N279" s="278" t="n">
+        <x:v>101</x:v>
+      </x:c>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="266" t="n">
@@ -16955,6 +17653,9 @@
       <x:c r="M280" s="242" t="n">
         <x:v>0.0125</x:v>
       </x:c>
+      <x:c r="N280" s="278" t="n">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="266" t="n">
@@ -16992,6 +17693,9 @@
       <x:c r="M281" s="242" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N281" s="278" t="n">
+        <x:v>101</x:v>
+      </x:c>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="266" t="n">
@@ -17029,6 +17733,9 @@
       <x:c r="M282" s="242" t="n">
         <x:v>0.017361111111111112</x:v>
       </x:c>
+      <x:c r="N282" s="278" t="n">
+        <x:v>86</x:v>
+      </x:c>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="266" t="n">
@@ -17066,6 +17773,9 @@
       <x:c r="M283" s="242" t="n">
         <x:v>0.016666666666666666</x:v>
       </x:c>
+      <x:c r="N283" s="278" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="266" t="n">
@@ -17103,6 +17813,9 @@
       <x:c r="M284" s="242" t="n">
         <x:v>0.006944444444444444</x:v>
       </x:c>
+      <x:c r="N284" s="278" t="n">
+        <x:v>92</x:v>
+      </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="266" t="n">
@@ -17140,6 +17853,9 @@
       <x:c r="M285" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N285" s="278" t="n">
+        <x:v>76</x:v>
+      </x:c>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="266" t="n">
@@ -17177,6 +17893,9 @@
       <x:c r="M286" s="242" t="n">
         <x:v>0.002777777777777778</x:v>
       </x:c>
+      <x:c r="N286" s="278" t="n">
+        <x:v>126</x:v>
+      </x:c>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="266" t="n">
@@ -17214,6 +17933,9 @@
       <x:c r="M287" s="242" t="n">
         <x:v>0.00625</x:v>
       </x:c>
+      <x:c r="N287" s="278" t="n">
+        <x:v>85</x:v>
+      </x:c>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="266" t="n">
@@ -17251,6 +17973,9 @@
       <x:c r="M288" s="242" t="n">
         <x:v>0.015277777777777777</x:v>
       </x:c>
+      <x:c r="N288" s="278" t="n">
+        <x:v>97</x:v>
+      </x:c>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="266" t="n">
@@ -17288,6 +18013,9 @@
       <x:c r="M289" s="242" t="n">
         <x:v>0.009722222222222222</x:v>
       </x:c>
+      <x:c r="N289" s="278" t="n">
+        <x:v>220</x:v>
+      </x:c>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="266" t="n">
@@ -17325,6 +18053,9 @@
       <x:c r="M290" s="242" t="n">
         <x:v>0.022916666666666665</x:v>
       </x:c>
+      <x:c r="N290" s="278" t="n">
+        <x:v>89</x:v>
+      </x:c>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="266" t="n">
@@ -17362,6 +18093,9 @@
       <x:c r="M291" s="242" t="n">
         <x:v>0.009027777777777777</x:v>
       </x:c>
+      <x:c r="N291" s="278" t="n">
+        <x:v>118</x:v>
+      </x:c>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="266" t="n">
@@ -17399,6 +18133,9 @@
       <x:c r="M292" s="242" t="n">
         <x:v>0.007638888888888889</x:v>
       </x:c>
+      <x:c r="N292" s="278" t="n">
+        <x:v>176</x:v>
+      </x:c>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="266" t="n">
@@ -17435,6 +18172,9 @@
       </x:c>
       <x:c r="M293" s="242" t="n">
         <x:v>0.015277777777777777</x:v>
+      </x:c>
+      <x:c r="N293" s="278" t="n">
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -17470,6 +18210,9 @@
       </x:c>
       <x:c r="M294" s="247" t="n">
         <x:v>0.01875</x:v>
+      </x:c>
+      <x:c r="N294" s="279" t="n">
+        <x:v>135</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17491,9 +18234,14 @@
       <x:formula>$I190="Sim"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="N3:N294">
+    <x:cfRule type="cellIs" dxfId="14" priority="4" operator="greaterThan">
+      <x:formula>90</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1aea83019a2741d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ba91a90fd8e4cfd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18012,7 +18760,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07f8f525ca3c4171"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b09c86e67a5456c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19422,7 +20170,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32568fe70a844144"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f4f89a9a22f49c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20919,7 +21667,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b277e199ae84b11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra90d5ad4966643d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21604,7 +22352,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d56b397ee749bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1e997b37b444bd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22209,7 +22957,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f49fe193c9d4707"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15465e9fe2e44219"/>
   </x:tableParts>
 </x:worksheet>
 </file>